--- a/my_skus.xlsx
+++ b/my_skus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\busykids\00 code\daily carero feed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBBEC87-7C1D-41B2-8616-DACD757DD45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EDA9E0-E4B7-4FB9-8458-A60A7F90C561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15384" yWindow="1128" windowWidth="15336" windowHeight="15432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18720" yWindow="2196" windowWidth="11712" windowHeight="14328" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,16 +25,214 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
   <si>
     <t>SKU</t>
+  </si>
+  <si>
+    <t>MI06</t>
+  </si>
+  <si>
+    <t>MR03S</t>
+  </si>
+  <si>
+    <t>UG70100</t>
+  </si>
+  <si>
+    <t>2D98237</t>
+  </si>
+  <si>
+    <t>LE12242</t>
+  </si>
+  <si>
+    <t>TV607</t>
+  </si>
+  <si>
+    <t>LE12241</t>
+  </si>
+  <si>
+    <t>2D33825</t>
+  </si>
+  <si>
+    <t>2D98264</t>
+  </si>
+  <si>
+    <t>LE12424</t>
+  </si>
+  <si>
+    <t>2D33837</t>
+  </si>
+  <si>
+    <t>BJ488</t>
+  </si>
+  <si>
+    <t>LE11684</t>
+  </si>
+  <si>
+    <t>2D98233</t>
+  </si>
+  <si>
+    <t>V2351</t>
+  </si>
+  <si>
+    <t>LE11917</t>
+  </si>
+  <si>
+    <t>2D33877</t>
+  </si>
+  <si>
+    <t>M38-B0577</t>
+  </si>
+  <si>
+    <t>UG70087</t>
+  </si>
+  <si>
+    <t>BJT023</t>
+  </si>
+  <si>
+    <t>2D11925</t>
+  </si>
+  <si>
+    <t>BJT015</t>
+  </si>
+  <si>
+    <t>V1006S</t>
+  </si>
+  <si>
+    <t>V4093B</t>
+  </si>
+  <si>
+    <t>2D33834</t>
+  </si>
+  <si>
+    <t>PL137</t>
+  </si>
+  <si>
+    <t>LE11608</t>
+  </si>
+  <si>
+    <t>LE9878</t>
+  </si>
+  <si>
+    <t>V8296</t>
+  </si>
+  <si>
+    <t>LE11005</t>
+  </si>
+  <si>
+    <t>2D33829</t>
+  </si>
+  <si>
+    <t>2D33899</t>
+  </si>
+  <si>
+    <t>2D33898</t>
+  </si>
+  <si>
+    <t>2D98268</t>
+  </si>
+  <si>
+    <t>2D33831</t>
+  </si>
+  <si>
+    <t>2D98221</t>
+  </si>
+  <si>
+    <t>2D98222</t>
+  </si>
+  <si>
+    <t>2D33819</t>
+  </si>
+  <si>
+    <t>M38-B1122</t>
+  </si>
+  <si>
+    <t>TV439</t>
+  </si>
+  <si>
+    <t>LE10947</t>
+  </si>
+  <si>
+    <t>TV317</t>
+  </si>
+  <si>
+    <t>PL103</t>
+  </si>
+  <si>
+    <t>LE11665</t>
+  </si>
+  <si>
+    <t>T0067</t>
+  </si>
+  <si>
+    <t>PL112</t>
+  </si>
+  <si>
+    <t>LE10616</t>
+  </si>
+  <si>
+    <t>2D98179</t>
+  </si>
+  <si>
+    <t>2D33820</t>
+  </si>
+  <si>
+    <t>T0068</t>
+  </si>
+  <si>
+    <t>JT154</t>
+  </si>
+  <si>
+    <t>2D33818</t>
+  </si>
+  <si>
+    <t>V8370</t>
+  </si>
+  <si>
+    <t>UG70158</t>
+  </si>
+  <si>
+    <t>H118</t>
+  </si>
+  <si>
+    <t>UG70157</t>
+  </si>
+  <si>
+    <t>JEMLE50400</t>
+  </si>
+  <si>
+    <t>LE12328</t>
+  </si>
+  <si>
+    <t>LE12622</t>
+  </si>
+  <si>
+    <t>TV453</t>
+  </si>
+  <si>
+    <t>LE12310</t>
+  </si>
+  <si>
+    <t>TV338</t>
+  </si>
+  <si>
+    <t>2D98265</t>
+  </si>
+  <si>
+    <t>UG70159</t>
+  </si>
+  <si>
+    <t>UG70160</t>
+  </si>
+  <si>
+    <t>UG70161</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -43,8 +241,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="14"/>
-      <color rgb="FF92D050"/>
+      <color theme="0"/>
       <name val="Medodica"/>
       <family val="3"/>
     </font>
@@ -77,11 +282,15 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,71 +571,364 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="8.88671875" style="3"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="19" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="2"/>
+    <col min="3" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>59125</v>
+      <c r="A2" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>59126</v>
+      <c r="A3" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>59290</v>
+      <c r="A4" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>58418</v>
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E8" s="3"/>
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E10" s="3"/>
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E11" s="3"/>
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E12" s="3"/>
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E13" s="3"/>
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E15" s="3"/>
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E18" s="3"/>
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
